--- a/textbook_examples/mod01_references_practice.xlsx
+++ b/textbook_examples/mod01_references_practice.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Relative referencing example" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Absolute referencing example" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Absolute referencing example 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ex1 (relative)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ex2 (absolute)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ex3 (absolute)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/textbook_examples/mod01_references_practice.xlsx
+++ b/textbook_examples/mod01_references_practice.xlsx
@@ -753,14 +753,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -773,28 +773,12 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Now each crop has its own conversion factor, sitting side by side in row 4.  We want one formula that fills all three columns.  Writing $B7*C$4 locks the column on the bushels (so every crop reads column B) and locks the row on the factors (so every load reads row 4) — but leaves the other half of each free to move.</t>
+          <t>Now we have two crops, and each has its own conversion factor.  The factors sit in row 14, directly underneath the column they belong to.  Writing B7*B$14 locks the row (so every load reads row 14) but leaves the column free — so the wheat column reads B14 and the barley column reads C14.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Tonnes per bushel →</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="11" t="n">
-        <v>0.027216</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>0.021772</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0.017237</v>
-      </c>
-    </row>
+    <row r="4" ht="18" customHeight="1"/>
     <row r="5" ht="18" customHeight="1"/>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -804,22 +788,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bushels</t>
+          <t>Wheat_bu</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>wheat_tons</t>
+          <t>Barley_bu</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>barley_tons</t>
+          <t>Wheat_tons</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>oats_tons</t>
+          <t>Barley_tons</t>
         </is>
       </c>
     </row>
@@ -832,7 +816,9 @@
       <c r="B7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C7" s="13" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>200</v>
+      </c>
       <c r="D7" s="13" t="n"/>
       <c r="E7" s="13" t="n"/>
     </row>
@@ -845,7 +831,9 @@
       <c r="B8" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="C8" s="13" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>300</v>
+      </c>
       <c r="D8" s="13" t="n"/>
       <c r="E8" s="13" t="n"/>
     </row>
@@ -858,7 +846,9 @@
       <c r="B9" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="C9" s="13" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>600</v>
+      </c>
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="13" t="n"/>
     </row>
@@ -871,7 +861,9 @@
       <c r="B10" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>800</v>
+      </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
     </row>
@@ -884,13 +876,28 @@
       <c r="B11" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="C11" s="13" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>1500</v>
+      </c>
       <c r="D11" s="13" t="n"/>
       <c r="E11" s="13" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1"/>
     <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Tons/bu</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.027216</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.021772</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>

--- a/textbook_examples/mod01_references_practice.xlsx
+++ b/textbook_examples/mod01_references_practice.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Relative referencing example" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Absolute referencing example" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Absolute referencing example 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ex1 (relative)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ex2 (absolute)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ex3 (absolute)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,14 +753,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -773,28 +773,12 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Now each crop has its own conversion factor, sitting side by side in row 4.  We want one formula that fills all three columns.  Writing $B7*C$4 locks the column on the bushels (so every crop reads column B) and locks the row on the factors (so every load reads row 4) — but leaves the other half of each free to move.</t>
+          <t>Now we have two crops, and each has its own conversion factor.  The factors sit in row 14, directly underneath the column they belong to.  Writing B7*B$14 locks the row (so every load reads row 14) but leaves the column free — so the wheat column reads B14 and the barley column reads C14.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Tonnes per bushel →</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="11" t="n">
-        <v>0.027216</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>0.021772</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0.017237</v>
-      </c>
-    </row>
+    <row r="4" ht="18" customHeight="1"/>
     <row r="5" ht="18" customHeight="1"/>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -804,22 +788,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bushels</t>
+          <t>Wheat_bu</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>wheat_tons</t>
+          <t>Barley_bu</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>barley_tons</t>
+          <t>Wheat_tons</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>oats_tons</t>
+          <t>Barley_tons</t>
         </is>
       </c>
     </row>
@@ -832,7 +816,9 @@
       <c r="B7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C7" s="13" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>200</v>
+      </c>
       <c r="D7" s="13" t="n"/>
       <c r="E7" s="13" t="n"/>
     </row>
@@ -845,7 +831,9 @@
       <c r="B8" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="C8" s="13" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>300</v>
+      </c>
       <c r="D8" s="13" t="n"/>
       <c r="E8" s="13" t="n"/>
     </row>
@@ -858,7 +846,9 @@
       <c r="B9" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="C9" s="13" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>600</v>
+      </c>
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="13" t="n"/>
     </row>
@@ -871,7 +861,9 @@
       <c r="B10" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>800</v>
+      </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
     </row>
@@ -884,13 +876,28 @@
       <c r="B11" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="C11" s="13" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>1500</v>
+      </c>
       <c r="D11" s="13" t="n"/>
       <c r="E11" s="13" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1"/>
     <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Tons/bu</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.027216</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.021772</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
